--- a/data/Books.xlsx
+++ b/data/Books.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Downloads\workspace_python\bookloader\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24FC5E6-F3B4-423D-9BDC-53654A285D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FDFE14-2837-4097-9ADE-9BE85D386F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="855" windowWidth="21600" windowHeight="12960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6495" yWindow="1245" windowWidth="21600" windowHeight="12960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="도서목록" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4442" uniqueCount="1656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4443" uniqueCount="1657">
   <si>
     <t>BOOKS</t>
   </si>
@@ -12156,6 +12156,10 @@
   </si>
   <si>
     <t>책 이름</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
 </sst>
@@ -12839,17 +12843,17 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13873,10 +13877,10 @@
         <f>COUNTA($B$15:B2108)</f>
         <v>559</v>
       </c>
-      <c r="C1" s="112" t="s">
+      <c r="C1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="113"/>
+      <c r="D1" s="115"/>
       <c r="E1" s="2">
         <f ca="1">COUNTBLANK($E$15:E2108)</f>
         <v>1535</v>
@@ -13897,7 +13901,7 @@
     </row>
     <row r="2" spans="1:17" ht="21" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="114" t="s">
+      <c r="B2" s="112" t="s">
         <v>1655</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -13917,9 +13921,8 @@
       <c r="G2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="7" t="str">
-        <f>CONCATENATE("미보유","(",H1,")")</f>
-        <v>미보유(309)</v>
+      <c r="H2" s="112" t="s">
+        <v>1656</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>4</v>
@@ -29566,14 +29569,14 @@
     <row r="1" spans="1:7" ht="23.25" customHeight="1">
       <c r="A1" s="31"/>
       <c r="B1" s="3"/>
-      <c r="C1" s="112" t="s">
+      <c r="C1" s="114" t="s">
         <v>1303</v>
       </c>
-      <c r="D1" s="113"/>
+      <c r="D1" s="115"/>
     </row>
     <row r="2" spans="1:7" ht="21" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="113" t="s">
         <v>1655</v>
       </c>
       <c r="C2" s="32" t="s">
